--- a/rejection_data.xlsx
+++ b/rejection_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Admin\Desktop\PistonRodPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C106E7BC-B7FB-41DF-94B2-0EF4BA246A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CE5709-106C-4B2A-A94A-2D6E9B33672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{2FF8ABF7-B34E-4442-953A-A8AB69CBC555}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2FF8ABF7-B34E-4442-953A-A8AB69CBC555}"/>
   </bookViews>
   <sheets>
     <sheet name="May-2026 Report" sheetId="1" r:id="rId1"/>
@@ -486,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -583,9 +583,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1207,31 +1204,31 @@
                   <c:v>8.0067567567567561</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>8.1020339363973495</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>16.54494382022472</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>10.598791755508174</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>8.1225285737500688</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>12.099227708869646</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>11.976187308766795</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>13.121998078770414</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>10.06338028169014</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>9.7628304821150849</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -1690,31 +1687,31 @@
                   <c:v>0.65540540540540537</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>2.2418249241487809</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.5407303370786517</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>0.83066808813077475</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.6608526082010725</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>0.5289024104844372</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>0.35253425568710922</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>0.40666026256804355</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>0.27464788732394368</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>0.90590979782270609</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -3564,25 +3561,25 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
+      <c r="H1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
@@ -3594,12 +3591,12 @@
       <c r="AG1" s="3"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
-      <c r="AJ1" s="77" t="s">
+      <c r="AJ1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="AK1" s="77"/>
-      <c r="AL1" s="77"/>
-      <c r="AM1" s="77"/>
+      <c r="AK1" s="76"/>
+      <c r="AL1" s="76"/>
+      <c r="AM1" s="76"/>
       <c r="AN1" s="5"/>
       <c r="AO1" s="5"/>
     </row>
@@ -3875,14 +3872,14 @@
       </c>
       <c r="D5" s="21">
         <f>AM5/AM22*100</f>
-        <v>1.3834343554099915</v>
+        <v>1.396017286126338</v>
       </c>
       <c r="E5" s="22">
         <v>1.74</v>
       </c>
       <c r="F5" s="23">
         <f>SUM(H5:AL5)</f>
-        <v>3734</v>
+        <v>6955</v>
       </c>
       <c r="G5" s="24">
         <v>15722</v>
@@ -3930,15 +3927,42 @@
       <c r="S5" s="25">
         <v>180</v>
       </c>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="26"/>
+      <c r="T5" s="25">
+        <f>75+42+82</f>
+        <v>199</v>
+      </c>
+      <c r="U5" s="25">
+        <f>80+104+80+70+66</f>
+        <v>400</v>
+      </c>
+      <c r="V5" s="25">
+        <f>104+145+91</f>
+        <v>340</v>
+      </c>
+      <c r="W5" s="25">
+        <f>43+80+130+105</f>
+        <v>358</v>
+      </c>
+      <c r="X5" s="25">
+        <f>116+80+84+87</f>
+        <v>367</v>
+      </c>
+      <c r="Y5" s="25">
+        <f>56+87+40+188</f>
+        <v>371</v>
+      </c>
+      <c r="Z5" s="25">
+        <f>251+177+83+134</f>
+        <v>645</v>
+      </c>
+      <c r="AA5" s="25">
+        <f>122+54</f>
+        <v>176</v>
+      </c>
+      <c r="AB5" s="25">
+        <f>96+65+74+130</f>
+        <v>365</v>
+      </c>
       <c r="AC5" s="26"/>
       <c r="AD5" s="26"/>
       <c r="AE5" s="25"/>
@@ -3951,7 +3975,7 @@
       <c r="AL5" s="25"/>
       <c r="AM5" s="25">
         <f>SUM(H5:AL5)</f>
-        <v>3734</v>
+        <v>6955</v>
       </c>
     </row>
     <row r="6" spans="2:175" s="31" customFormat="1" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4010,15 +4034,33 @@
       <c r="S6" s="29">
         <v>0</v>
       </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
+      <c r="T6" s="29">
+        <v>0</v>
+      </c>
+      <c r="U6" s="29">
+        <v>0</v>
+      </c>
+      <c r="V6" s="29">
+        <v>0</v>
+      </c>
+      <c r="W6" s="29">
+        <v>0</v>
+      </c>
+      <c r="X6" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="29">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="29">
+        <v>0</v>
+      </c>
       <c r="AC6" s="29"/>
       <c r="AD6" s="29"/>
       <c r="AE6" s="29"/>
@@ -4178,7 +4220,7 @@
       </c>
       <c r="D7" s="21">
         <f>AM7/AM24*100</f>
-        <v>133.97015666201335</v>
+        <v>133.32075597926075</v>
       </c>
       <c r="E7" s="22">
         <v>0.33</v>
@@ -4224,15 +4266,33 @@
       <c r="S7" s="33">
         <v>0</v>
       </c>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="34"/>
+      <c r="T7" s="34">
+        <v>0</v>
+      </c>
+      <c r="U7" s="33">
+        <v>0</v>
+      </c>
+      <c r="V7" s="33">
+        <v>0</v>
+      </c>
+      <c r="W7" s="33">
+        <v>0</v>
+      </c>
+      <c r="X7" s="33">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="33">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="33">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="33">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="33">
+        <v>0</v>
+      </c>
       <c r="AC7" s="34"/>
       <c r="AD7" s="34"/>
       <c r="AE7" s="33"/>
@@ -4249,7 +4309,7 @@
       </c>
     </row>
     <row r="8" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="35" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="20">
@@ -4258,14 +4318,14 @@
       </c>
       <c r="D8" s="21">
         <f>AM8/AM22*100</f>
-        <v>1.6701987343835676</v>
+        <v>1.7366414895133107</v>
       </c>
       <c r="E8" s="22">
         <v>0.51</v>
       </c>
       <c r="F8" s="23">
         <f t="shared" si="1"/>
-        <v>4508</v>
+        <v>8652</v>
       </c>
       <c r="G8" s="24">
         <v>4592</v>
@@ -4299,7 +4359,7 @@
         <f>115+129+90+211</f>
         <v>545</v>
       </c>
-      <c r="P8" s="37">
+      <c r="P8" s="36">
         <f>136+0</f>
         <v>136</v>
       </c>
@@ -4310,20 +4370,47 @@
       <c r="R8" s="30">
         <v>218</v>
       </c>
-      <c r="S8" s="37">
+      <c r="S8" s="36">
         <v>146</v>
       </c>
-      <c r="T8" s="30"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="39"/>
+      <c r="T8" s="30">
+        <f>85+60</f>
+        <v>145</v>
+      </c>
+      <c r="U8" s="30">
+        <f>97+30+35+277+415</f>
+        <v>854</v>
+      </c>
+      <c r="V8" s="30">
+        <f>145+103</f>
+        <v>248</v>
+      </c>
+      <c r="W8" s="30">
+        <f>171+550+90</f>
+        <v>811</v>
+      </c>
+      <c r="X8" s="30">
+        <f>250+44+98</f>
+        <v>392</v>
+      </c>
+      <c r="Y8" s="30">
+        <f>210+111+377</f>
+        <v>698</v>
+      </c>
+      <c r="Z8" s="30">
+        <f>115+129+90+211</f>
+        <v>545</v>
+      </c>
+      <c r="AA8" s="36">
+        <f>136+0</f>
+        <v>136</v>
+      </c>
+      <c r="AB8" s="30">
+        <f>158+87+70</f>
+        <v>315</v>
+      </c>
+      <c r="AC8" s="38"/>
+      <c r="AD8" s="38"/>
       <c r="AE8" s="30"/>
       <c r="AF8" s="30"/>
       <c r="AG8" s="30"/>
@@ -4334,11 +4421,11 @@
       <c r="AL8" s="30"/>
       <c r="AM8" s="30">
         <f t="shared" si="2"/>
-        <v>4508</v>
+        <v>8652</v>
       </c>
     </row>
     <row r="9" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="35" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="20">
@@ -4347,20 +4434,20 @@
       </c>
       <c r="D9" s="21">
         <f>AM9/AM22*100</f>
-        <v>0.29528580108777802</v>
+        <v>0.29606405421083376</v>
       </c>
       <c r="E9" s="22">
         <v>0.35</v>
       </c>
       <c r="F9" s="23">
         <f t="shared" si="1"/>
-        <v>797</v>
+        <v>1475</v>
       </c>
       <c r="G9" s="24">
         <v>5267</v>
       </c>
       <c r="H9" s="30"/>
-      <c r="I9" s="39">
+      <c r="I9" s="38">
         <f>45+18</f>
         <v>63</v>
       </c>
@@ -4402,17 +4489,44 @@
       <c r="S9" s="30">
         <v>26</v>
       </c>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="39"/>
+      <c r="T9" s="38">
+        <f>45+18</f>
+        <v>63</v>
+      </c>
+      <c r="U9" s="30">
+        <f>27+51+10+4+16</f>
+        <v>108</v>
+      </c>
+      <c r="V9" s="30">
+        <f>10+16+67</f>
+        <v>93</v>
+      </c>
+      <c r="W9" s="30">
+        <f>32+24+23+2</f>
+        <v>81</v>
+      </c>
+      <c r="X9" s="30">
+        <f>16+19+24</f>
+        <v>59</v>
+      </c>
+      <c r="Y9" s="30">
+        <f>14+40+39</f>
+        <v>93</v>
+      </c>
+      <c r="Z9" s="30">
+        <f>20+3+50+13</f>
+        <v>86</v>
+      </c>
+      <c r="AA9" s="30">
+        <f>12+15</f>
+        <v>27</v>
+      </c>
+      <c r="AB9" s="30">
+        <f>2+7+59</f>
+        <v>68</v>
+      </c>
+      <c r="AC9" s="38"/>
+      <c r="AD9" s="38"/>
       <c r="AE9" s="30"/>
       <c r="AF9" s="30"/>
       <c r="AG9" s="30"/>
@@ -4423,11 +4537,11 @@
       <c r="AL9" s="30"/>
       <c r="AM9" s="30">
         <f t="shared" si="2"/>
-        <v>797</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="10" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="20">
@@ -4436,14 +4550,14 @@
       </c>
       <c r="D10" s="21">
         <f>AM10/AM22*100</f>
-        <v>0.18487781021681463</v>
+        <v>0.18105069620215053</v>
       </c>
       <c r="E10" s="22">
         <v>0.88</v>
       </c>
       <c r="F10" s="23">
         <f t="shared" si="1"/>
-        <v>499</v>
+        <v>902</v>
       </c>
       <c r="G10" s="24">
         <v>7891</v>
@@ -4485,17 +4599,38 @@
       <c r="S10" s="30">
         <v>30</v>
       </c>
-      <c r="T10" s="30"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="39"/>
-      <c r="AC10" s="39"/>
-      <c r="AD10" s="39"/>
+      <c r="T10" s="30">
+        <v>0</v>
+      </c>
+      <c r="U10" s="30">
+        <v>29</v>
+      </c>
+      <c r="V10" s="30">
+        <v>0</v>
+      </c>
+      <c r="W10" s="30">
+        <f>13+10+22</f>
+        <v>45</v>
+      </c>
+      <c r="X10" s="30">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="30">
+        <f>27+8</f>
+        <v>35</v>
+      </c>
+      <c r="Z10" s="30">
+        <f>16+138+31</f>
+        <v>185</v>
+      </c>
+      <c r="AA10" s="30">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="30">
+        <v>94</v>
+      </c>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="38"/>
       <c r="AE10" s="30"/>
       <c r="AF10" s="30"/>
       <c r="AG10" s="30"/>
@@ -4506,11 +4641,11 @@
       <c r="AL10" s="30"/>
       <c r="AM10" s="30">
         <f t="shared" si="2"/>
-        <v>499</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="35" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="20">
@@ -4519,16 +4654,16 @@
       </c>
       <c r="D11" s="21">
         <f>AM11/AM22*100</f>
-        <v>5.8682958637758045</v>
+        <v>5.8729072285795141</v>
       </c>
       <c r="E11" s="22">
         <v>0.59</v>
       </c>
       <c r="F11" s="23">
         <f t="shared" si="1"/>
-        <v>15839</v>
-      </c>
-      <c r="G11" s="40">
+        <v>29259</v>
+      </c>
+      <c r="G11" s="39">
         <v>5291</v>
       </c>
       <c r="H11" s="30"/>
@@ -4574,17 +4709,44 @@
       <c r="S11" s="30">
         <v>620</v>
       </c>
-      <c r="T11" s="30"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
+      <c r="T11" s="30">
+        <f>210+400+215</f>
+        <v>825</v>
+      </c>
+      <c r="U11" s="30">
+        <f>585+350+1000+800+180</f>
+        <v>2915</v>
+      </c>
+      <c r="V11" s="30">
+        <f>285+385+540</f>
+        <v>1210</v>
+      </c>
+      <c r="W11" s="30">
+        <f>142+60+500+600</f>
+        <v>1302</v>
+      </c>
+      <c r="X11" s="30">
+        <f>742+69+205+131</f>
+        <v>1147</v>
+      </c>
+      <c r="Y11" s="30">
+        <f>232+355+700+231</f>
+        <v>1518</v>
+      </c>
+      <c r="Z11" s="30">
+        <f>180+550+650+858</f>
+        <v>2238</v>
+      </c>
+      <c r="AA11" s="30">
+        <f>500+486</f>
+        <v>986</v>
+      </c>
+      <c r="AB11" s="30">
+        <f>300+350+139+490</f>
+        <v>1279</v>
+      </c>
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
       <c r="AE11" s="30"/>
       <c r="AF11" s="30"/>
       <c r="AG11" s="30"/>
@@ -4595,11 +4757,11 @@
       <c r="AL11" s="30"/>
       <c r="AM11" s="30">
         <f t="shared" si="2"/>
-        <v>15839</v>
+        <v>29259</v>
       </c>
     </row>
     <row r="12" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="40" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="20">
@@ -4608,16 +4770,16 @@
       </c>
       <c r="D12" s="21">
         <f>AM12/AM22*100</f>
-        <v>0.93920891563051101</v>
+        <v>0.86852146614934067</v>
       </c>
       <c r="E12" s="22">
         <v>0.57999999999999996</v>
       </c>
       <c r="F12" s="23">
         <f t="shared" si="1"/>
-        <v>2535</v>
-      </c>
-      <c r="G12" s="40">
+        <v>4327</v>
+      </c>
+      <c r="G12" s="39">
         <v>5214</v>
       </c>
       <c r="H12" s="30"/>
@@ -4660,32 +4822,56 @@
       <c r="S12" s="30">
         <v>0</v>
       </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
+      <c r="T12" s="30">
+        <f>100+55</f>
+        <v>155</v>
+      </c>
+      <c r="U12" s="30">
+        <f>300+241</f>
+        <v>541</v>
+      </c>
+      <c r="V12" s="30">
+        <f>69+0</f>
+        <v>69</v>
+      </c>
+      <c r="W12" s="30">
+        <v>60</v>
+      </c>
+      <c r="X12" s="30">
+        <f>100+41</f>
+        <v>141</v>
+      </c>
+      <c r="Y12" s="30">
+        <f>137+89+100</f>
+        <v>326</v>
+      </c>
+      <c r="Z12" s="30">
+        <f>100+200</f>
+        <v>300</v>
+      </c>
+      <c r="AA12" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="30">
+        <v>200</v>
+      </c>
+      <c r="AC12" s="38"/>
+      <c r="AD12" s="38"/>
       <c r="AE12" s="30"/>
       <c r="AF12" s="30"/>
       <c r="AG12" s="30"/>
-      <c r="AH12" s="42"/>
-      <c r="AI12" s="42"/>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42">
+      <c r="AH12" s="41"/>
+      <c r="AI12" s="41"/>
+      <c r="AJ12" s="41"/>
+      <c r="AK12" s="41"/>
+      <c r="AL12" s="41"/>
+      <c r="AM12" s="41">
         <f t="shared" si="2"/>
-        <v>2535</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="13" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="35" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="20">
@@ -4694,16 +4880,16 @@
       </c>
       <c r="D13" s="21">
         <f>AM13/AM22*100</f>
-        <v>1.2222683284674778</v>
+        <v>1.2727743510175571</v>
       </c>
       <c r="E13" s="22">
         <v>0.36</v>
       </c>
       <c r="F13" s="23">
         <f t="shared" si="1"/>
-        <v>3299</v>
-      </c>
-      <c r="G13" s="40">
+        <v>6341</v>
+      </c>
+      <c r="G13" s="39">
         <v>3248</v>
       </c>
       <c r="H13" s="30"/>
@@ -4749,17 +4935,44 @@
       <c r="S13" s="30">
         <v>102</v>
       </c>
-      <c r="T13" s="30"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
+      <c r="T13" s="30">
+        <f>45+17+27</f>
+        <v>89</v>
+      </c>
+      <c r="U13" s="30">
+        <f>80+54+60+30+17</f>
+        <v>241</v>
+      </c>
+      <c r="V13" s="30">
+        <f>43+10+345</f>
+        <v>398</v>
+      </c>
+      <c r="W13" s="30">
+        <f>191+45+41</f>
+        <v>277</v>
+      </c>
+      <c r="X13" s="30">
+        <f>0+286+201+39+30</f>
+        <v>556</v>
+      </c>
+      <c r="Y13" s="30">
+        <f>464+149+56+60</f>
+        <v>729</v>
+      </c>
+      <c r="Z13" s="30">
+        <f>249+63+40</f>
+        <v>352</v>
+      </c>
+      <c r="AA13" s="30">
+        <f>26+40</f>
+        <v>66</v>
+      </c>
+      <c r="AB13" s="30">
+        <f>30+25+40+239</f>
+        <v>334</v>
+      </c>
+      <c r="AC13" s="38"/>
+      <c r="AD13" s="38"/>
       <c r="AE13" s="30"/>
       <c r="AF13" s="30"/>
       <c r="AG13" s="30"/>
@@ -4770,11 +4983,11 @@
       <c r="AL13" s="30"/>
       <c r="AM13" s="30">
         <f t="shared" si="2"/>
-        <v>3299</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="14" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="35" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="20">
@@ -4785,9 +4998,9 @@
       <c r="E14" s="22"/>
       <c r="F14" s="23">
         <f t="shared" si="1"/>
-        <v>352</v>
-      </c>
-      <c r="G14" s="40"/>
+        <v>704</v>
+      </c>
+      <c r="G14" s="39"/>
       <c r="H14" s="30"/>
       <c r="I14" s="30">
         <v>0</v>
@@ -4823,17 +5036,36 @@
       <c r="S14" s="30">
         <v>0</v>
       </c>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="30"/>
-      <c r="Y14" s="30"/>
-      <c r="Z14" s="30"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="39"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="39"/>
+      <c r="T14" s="30">
+        <v>0</v>
+      </c>
+      <c r="U14" s="30">
+        <v>0</v>
+      </c>
+      <c r="V14" s="30">
+        <v>0</v>
+      </c>
+      <c r="W14" s="30">
+        <v>0</v>
+      </c>
+      <c r="X14" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="30">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="30">
+        <f>40+63+249</f>
+        <v>352</v>
+      </c>
+      <c r="AA14" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="38"/>
+      <c r="AD14" s="38"/>
       <c r="AE14" s="30"/>
       <c r="AF14" s="30"/>
       <c r="AG14" s="30"/>
@@ -4844,7 +5076,7 @@
       <c r="AL14" s="30"/>
       <c r="AM14" s="30">
         <f t="shared" si="2"/>
-        <v>352</v>
+        <v>704</v>
       </c>
     </row>
     <row r="15" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4857,16 +5089,16 @@
       </c>
       <c r="D15" s="21">
         <f>AM15/AM22*100</f>
-        <v>0.37346058657023878</v>
+        <v>0.37394395457273444</v>
       </c>
       <c r="E15" s="22">
         <v>0.17</v>
       </c>
       <c r="F15" s="23">
         <f t="shared" si="1"/>
-        <v>1008</v>
-      </c>
-      <c r="G15" s="40">
+        <v>1863</v>
+      </c>
+      <c r="G15" s="39">
         <v>1489</v>
       </c>
       <c r="H15" s="30"/>
@@ -4912,17 +5144,44 @@
       <c r="S15" s="30">
         <v>81</v>
       </c>
-      <c r="T15" s="30"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="30"/>
-      <c r="X15" s="30"/>
-      <c r="Y15" s="30"/>
-      <c r="Z15" s="30"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="39"/>
+      <c r="T15" s="30">
+        <f>28+13+80</f>
+        <v>121</v>
+      </c>
+      <c r="U15" s="30">
+        <f>10+30+100+25</f>
+        <v>165</v>
+      </c>
+      <c r="V15" s="30">
+        <f>55+11+31</f>
+        <v>97</v>
+      </c>
+      <c r="W15" s="30">
+        <f>25+73+27</f>
+        <v>125</v>
+      </c>
+      <c r="X15" s="30">
+        <f>5+23+26</f>
+        <v>54</v>
+      </c>
+      <c r="Y15" s="30">
+        <f>103+4+50</f>
+        <v>157</v>
+      </c>
+      <c r="Z15" s="30">
+        <f>20+27</f>
+        <v>47</v>
+      </c>
+      <c r="AA15" s="30">
+        <f>10+23</f>
+        <v>33</v>
+      </c>
+      <c r="AB15" s="30">
+        <f>16+20+20</f>
+        <v>56</v>
+      </c>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
       <c r="AE15" s="30"/>
       <c r="AF15" s="30"/>
       <c r="AG15" s="30"/>
@@ -4933,11 +5192,11 @@
       <c r="AL15" s="30"/>
       <c r="AM15" s="30">
         <f t="shared" si="2"/>
-        <v>1008</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="16" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="42" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="20">
@@ -4954,69 +5213,87 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="39">
         <v>17</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38">
-        <v>0</v>
-      </c>
-      <c r="J16" s="38">
-        <v>0</v>
-      </c>
-      <c r="K16" s="38">
-        <v>0</v>
-      </c>
-      <c r="L16" s="38">
-        <v>0</v>
-      </c>
-      <c r="M16" s="38">
-        <v>0</v>
-      </c>
-      <c r="N16" s="38">
-        <v>0</v>
-      </c>
-      <c r="O16" s="38">
-        <v>0</v>
-      </c>
-      <c r="P16" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="38">
-        <v>0</v>
-      </c>
-      <c r="R16" s="38">
-        <v>0</v>
-      </c>
-      <c r="S16" s="38">
-        <v>0</v>
-      </c>
-      <c r="T16" s="38"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="38"/>
-      <c r="Y16" s="38"/>
-      <c r="Z16" s="38"/>
-      <c r="AA16" s="38"/>
-      <c r="AB16" s="38"/>
-      <c r="AC16" s="38"/>
-      <c r="AD16" s="38"/>
-      <c r="AE16" s="38"/>
-      <c r="AF16" s="38"/>
-      <c r="AG16" s="38"/>
-      <c r="AH16" s="38"/>
-      <c r="AI16" s="38"/>
-      <c r="AJ16" s="38"/>
-      <c r="AK16" s="38"/>
-      <c r="AL16" s="38"/>
-      <c r="AM16" s="38">
+      <c r="H16" s="37"/>
+      <c r="I16" s="37">
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
+        <v>0</v>
+      </c>
+      <c r="K16" s="37">
+        <v>0</v>
+      </c>
+      <c r="L16" s="37">
+        <v>0</v>
+      </c>
+      <c r="M16" s="37">
+        <v>0</v>
+      </c>
+      <c r="N16" s="37">
+        <v>0</v>
+      </c>
+      <c r="O16" s="37">
+        <v>0</v>
+      </c>
+      <c r="P16" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="37">
+        <v>0</v>
+      </c>
+      <c r="R16" s="37">
+        <v>0</v>
+      </c>
+      <c r="S16" s="37">
+        <v>0</v>
+      </c>
+      <c r="T16" s="37">
+        <v>0</v>
+      </c>
+      <c r="U16" s="37">
+        <v>0</v>
+      </c>
+      <c r="V16" s="37">
+        <v>0</v>
+      </c>
+      <c r="W16" s="37">
+        <v>0</v>
+      </c>
+      <c r="X16" s="37">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="37">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="37">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="37">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="37"/>
+      <c r="AD16" s="37"/>
+      <c r="AE16" s="37"/>
+      <c r="AF16" s="37"/>
+      <c r="AG16" s="37"/>
+      <c r="AH16" s="37"/>
+      <c r="AI16" s="37"/>
+      <c r="AJ16" s="37"/>
+      <c r="AK16" s="37"/>
+      <c r="AL16" s="37"/>
+      <c r="AM16" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="42" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="20">
@@ -5025,7 +5302,7 @@
       </c>
       <c r="D17" s="21">
         <f>AM17/AM22*100</f>
-        <v>1.2967381478133288E-2</v>
+        <v>7.0252487439858855E-3</v>
       </c>
       <c r="E17" s="22">
         <v>0.01</v>
@@ -5034,69 +5311,87 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="39">
         <v>134</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38">
-        <v>0</v>
-      </c>
-      <c r="J17" s="38">
-        <v>0</v>
-      </c>
-      <c r="K17" s="38">
-        <v>0</v>
-      </c>
-      <c r="L17" s="38">
-        <v>0</v>
-      </c>
-      <c r="M17" s="38">
-        <v>0</v>
-      </c>
-      <c r="N17" s="38">
-        <v>0</v>
-      </c>
-      <c r="O17" s="38">
-        <v>0</v>
-      </c>
-      <c r="P17" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="38">
-        <v>0</v>
-      </c>
-      <c r="R17" s="38">
+      <c r="H17" s="37"/>
+      <c r="I17" s="37">
+        <v>0</v>
+      </c>
+      <c r="J17" s="37">
+        <v>0</v>
+      </c>
+      <c r="K17" s="37">
+        <v>0</v>
+      </c>
+      <c r="L17" s="37">
+        <v>0</v>
+      </c>
+      <c r="M17" s="37">
+        <v>0</v>
+      </c>
+      <c r="N17" s="37">
+        <v>0</v>
+      </c>
+      <c r="O17" s="37">
+        <v>0</v>
+      </c>
+      <c r="P17" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="37">
+        <v>0</v>
+      </c>
+      <c r="R17" s="37">
         <v>23</v>
       </c>
-      <c r="S17" s="38">
+      <c r="S17" s="37">
         <v>12</v>
       </c>
-      <c r="T17" s="38"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="38"/>
-      <c r="AB17" s="44"/>
-      <c r="AC17" s="44"/>
-      <c r="AD17" s="44"/>
-      <c r="AE17" s="38"/>
-      <c r="AF17" s="38"/>
-      <c r="AG17" s="38"/>
-      <c r="AH17" s="38"/>
-      <c r="AI17" s="38"/>
-      <c r="AJ17" s="38"/>
-      <c r="AK17" s="38"/>
-      <c r="AL17" s="38"/>
-      <c r="AM17" s="38">
+      <c r="T17" s="37">
+        <v>0</v>
+      </c>
+      <c r="U17" s="37">
+        <v>0</v>
+      </c>
+      <c r="V17" s="37">
+        <v>0</v>
+      </c>
+      <c r="W17" s="37">
+        <v>0</v>
+      </c>
+      <c r="X17" s="37">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="37">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="37">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="37">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="43"/>
+      <c r="AD17" s="43"/>
+      <c r="AE17" s="37"/>
+      <c r="AF17" s="37"/>
+      <c r="AG17" s="37"/>
+      <c r="AH17" s="37"/>
+      <c r="AI17" s="37"/>
+      <c r="AJ17" s="37"/>
+      <c r="AK17" s="37"/>
+      <c r="AL17" s="37"/>
+      <c r="AM17" s="37">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="42" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="20">
@@ -5105,87 +5400,114 @@
       </c>
       <c r="D18" s="21">
         <f>AM18/AM22*100</f>
-        <v>0.24045230226595729</v>
+        <v>0.22942455183931049</v>
       </c>
       <c r="E18" s="22">
         <v>0.21</v>
       </c>
       <c r="F18" s="23">
         <f t="shared" si="1"/>
-        <v>649</v>
-      </c>
-      <c r="G18" s="40">
+        <v>1143</v>
+      </c>
+      <c r="G18" s="39">
         <v>1872</v>
       </c>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38">
+      <c r="H18" s="37"/>
+      <c r="I18" s="37">
         <f>20+19</f>
         <v>39</v>
       </c>
-      <c r="J18" s="38">
+      <c r="J18" s="37">
         <f>13+26</f>
         <v>39</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="37">
         <f>28+2+26</f>
         <v>56</v>
       </c>
-      <c r="L18" s="38">
+      <c r="L18" s="37">
         <f>73+36+15</f>
         <v>124</v>
       </c>
-      <c r="M18" s="38">
+      <c r="M18" s="37">
         <f>6+26+26</f>
         <v>58</v>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="37">
         <f>48+22</f>
         <v>70</v>
       </c>
-      <c r="O18" s="38">
+      <c r="O18" s="37">
         <f>16+20</f>
         <v>36</v>
       </c>
-      <c r="P18" s="38">
+      <c r="P18" s="37">
         <f>28+11</f>
         <v>39</v>
       </c>
-      <c r="Q18" s="38">
+      <c r="Q18" s="37">
         <f>20+13</f>
         <v>33</v>
       </c>
-      <c r="R18" s="38">
+      <c r="R18" s="37">
         <v>70</v>
       </c>
-      <c r="S18" s="38">
+      <c r="S18" s="37">
         <v>85</v>
       </c>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="38"/>
-      <c r="Y18" s="38"/>
-      <c r="Z18" s="38"/>
-      <c r="AA18" s="38"/>
-      <c r="AB18" s="44"/>
-      <c r="AC18" s="44"/>
-      <c r="AD18" s="44"/>
-      <c r="AE18" s="38"/>
-      <c r="AF18" s="38"/>
-      <c r="AG18" s="38"/>
-      <c r="AH18" s="38"/>
-      <c r="AI18" s="38"/>
-      <c r="AJ18" s="38"/>
-      <c r="AK18" s="38"/>
-      <c r="AL18" s="38"/>
-      <c r="AM18" s="38">
+      <c r="T18" s="37">
+        <f>20+19</f>
+        <v>39</v>
+      </c>
+      <c r="U18" s="37">
+        <f>13+26</f>
+        <v>39</v>
+      </c>
+      <c r="V18" s="37">
+        <f>28+2+26</f>
+        <v>56</v>
+      </c>
+      <c r="W18" s="37">
+        <f>73+36+15</f>
+        <v>124</v>
+      </c>
+      <c r="X18" s="37">
+        <f>6+26+26</f>
+        <v>58</v>
+      </c>
+      <c r="Y18" s="37">
+        <f>48+22</f>
+        <v>70</v>
+      </c>
+      <c r="Z18" s="37">
+        <f>16+20</f>
+        <v>36</v>
+      </c>
+      <c r="AA18" s="37">
+        <f>28+11</f>
+        <v>39</v>
+      </c>
+      <c r="AB18" s="37">
+        <f>20+13</f>
+        <v>33</v>
+      </c>
+      <c r="AC18" s="43"/>
+      <c r="AD18" s="43"/>
+      <c r="AE18" s="37"/>
+      <c r="AF18" s="37"/>
+      <c r="AG18" s="37"/>
+      <c r="AH18" s="37"/>
+      <c r="AI18" s="37"/>
+      <c r="AJ18" s="37"/>
+      <c r="AK18" s="37"/>
+      <c r="AL18" s="37"/>
+      <c r="AM18" s="37">
         <f t="shared" si="2"/>
-        <v>649</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="19" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="42" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="20">
@@ -5194,83 +5516,106 @@
       </c>
       <c r="D19" s="21">
         <f>AM19/AM22*100</f>
-        <v>0.42755309216473758</v>
+        <v>0.45403179025417351</v>
       </c>
       <c r="E19" s="22">
         <v>0.28000000000000003</v>
       </c>
       <c r="F19" s="23">
         <f t="shared" si="1"/>
-        <v>1154</v>
-      </c>
-      <c r="G19" s="40">
+        <v>2262</v>
+      </c>
+      <c r="G19" s="39">
         <v>2502</v>
       </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38">
+      <c r="H19" s="37"/>
+      <c r="I19" s="37">
         <v>360</v>
       </c>
-      <c r="J19" s="45">
+      <c r="J19" s="44">
         <f>30+85</f>
         <v>115</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="44">
         <f>101+25+5</f>
         <v>131</v>
       </c>
-      <c r="L19" s="45">
+      <c r="L19" s="44">
         <f>70+50</f>
         <v>120</v>
       </c>
-      <c r="M19" s="45">
+      <c r="M19" s="44">
         <v>55</v>
       </c>
-      <c r="N19" s="45">
+      <c r="N19" s="44">
         <f>35+1</f>
         <v>36</v>
       </c>
-      <c r="O19" s="45">
+      <c r="O19" s="44">
         <f>41+50</f>
         <v>91</v>
       </c>
-      <c r="P19" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="38">
+      <c r="P19" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="37">
         <v>200</v>
       </c>
-      <c r="R19" s="45">
+      <c r="R19" s="44">
         <v>46</v>
       </c>
-      <c r="S19" s="38">
-        <v>0</v>
-      </c>
-      <c r="T19" s="38"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="45"/>
-      <c r="Y19" s="38"/>
-      <c r="Z19" s="45"/>
-      <c r="AA19" s="38"/>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="44"/>
-      <c r="AE19" s="38"/>
-      <c r="AF19" s="38"/>
-      <c r="AG19" s="38"/>
-      <c r="AH19" s="38"/>
-      <c r="AI19" s="38"/>
-      <c r="AJ19" s="38"/>
-      <c r="AK19" s="38"/>
-      <c r="AL19" s="38"/>
-      <c r="AM19" s="38">
+      <c r="S19" s="37">
+        <v>0</v>
+      </c>
+      <c r="T19" s="37">
+        <v>360</v>
+      </c>
+      <c r="U19" s="44">
+        <f>30+85</f>
+        <v>115</v>
+      </c>
+      <c r="V19" s="44">
+        <f>101+25+5</f>
+        <v>131</v>
+      </c>
+      <c r="W19" s="44">
+        <f>70+50</f>
+        <v>120</v>
+      </c>
+      <c r="X19" s="44">
+        <v>55</v>
+      </c>
+      <c r="Y19" s="44">
+        <f>35+1</f>
+        <v>36</v>
+      </c>
+      <c r="Z19" s="44">
+        <f>41+50</f>
+        <v>91</v>
+      </c>
+      <c r="AA19" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="37">
+        <v>200</v>
+      </c>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="37"/>
+      <c r="AF19" s="37"/>
+      <c r="AG19" s="37"/>
+      <c r="AH19" s="37"/>
+      <c r="AI19" s="37"/>
+      <c r="AJ19" s="37"/>
+      <c r="AK19" s="37"/>
+      <c r="AL19" s="37"/>
+      <c r="AM19" s="37">
         <f t="shared" si="2"/>
-        <v>1154</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="42" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="20">
@@ -5287,69 +5632,87 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="39">
         <v>2</v>
       </c>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45">
-        <v>0</v>
-      </c>
-      <c r="J20" s="45">
-        <v>0</v>
-      </c>
-      <c r="K20" s="45">
-        <v>0</v>
-      </c>
-      <c r="L20" s="45">
-        <v>0</v>
-      </c>
-      <c r="M20" s="45">
-        <v>0</v>
-      </c>
-      <c r="N20" s="45">
-        <v>0</v>
-      </c>
-      <c r="O20" s="45">
-        <v>0</v>
-      </c>
-      <c r="P20" s="45">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="45">
-        <v>0</v>
-      </c>
-      <c r="R20" s="45">
-        <v>0</v>
-      </c>
-      <c r="S20" s="45">
-        <v>0</v>
-      </c>
-      <c r="T20" s="45"/>
-      <c r="U20" s="45"/>
-      <c r="V20" s="45"/>
-      <c r="W20" s="45"/>
-      <c r="X20" s="45"/>
-      <c r="Y20" s="45"/>
-      <c r="Z20" s="45"/>
-      <c r="AA20" s="45"/>
-      <c r="AB20" s="45"/>
-      <c r="AC20" s="45"/>
-      <c r="AD20" s="45"/>
-      <c r="AE20" s="45"/>
-      <c r="AF20" s="45"/>
-      <c r="AG20" s="45"/>
-      <c r="AH20" s="45"/>
-      <c r="AI20" s="45"/>
-      <c r="AJ20" s="45"/>
-      <c r="AK20" s="45"/>
-      <c r="AL20" s="45"/>
-      <c r="AM20" s="38">
+      <c r="H20" s="44"/>
+      <c r="I20" s="44">
+        <v>0</v>
+      </c>
+      <c r="J20" s="44">
+        <v>0</v>
+      </c>
+      <c r="K20" s="44">
+        <v>0</v>
+      </c>
+      <c r="L20" s="44">
+        <v>0</v>
+      </c>
+      <c r="M20" s="44">
+        <v>0</v>
+      </c>
+      <c r="N20" s="44">
+        <v>0</v>
+      </c>
+      <c r="O20" s="44">
+        <v>0</v>
+      </c>
+      <c r="P20" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="44">
+        <v>0</v>
+      </c>
+      <c r="R20" s="44">
+        <v>0</v>
+      </c>
+      <c r="S20" s="44">
+        <v>0</v>
+      </c>
+      <c r="T20" s="44">
+        <v>0</v>
+      </c>
+      <c r="U20" s="44">
+        <v>0</v>
+      </c>
+      <c r="V20" s="44">
+        <v>0</v>
+      </c>
+      <c r="W20" s="44">
+        <v>0</v>
+      </c>
+      <c r="X20" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="44"/>
+      <c r="AD20" s="44"/>
+      <c r="AE20" s="44"/>
+      <c r="AF20" s="44"/>
+      <c r="AG20" s="44"/>
+      <c r="AH20" s="44"/>
+      <c r="AI20" s="44"/>
+      <c r="AJ20" s="44"/>
+      <c r="AK20" s="44"/>
+      <c r="AL20" s="44"/>
+      <c r="AM20" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="42" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="20">
@@ -5366,84 +5729,102 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="39">
         <v>25</v>
       </c>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45">
-        <v>0</v>
-      </c>
-      <c r="J21" s="45">
-        <v>0</v>
-      </c>
-      <c r="K21" s="45">
-        <v>0</v>
-      </c>
-      <c r="L21" s="45">
-        <v>0</v>
-      </c>
-      <c r="M21" s="45">
-        <v>0</v>
-      </c>
-      <c r="N21" s="45">
-        <v>0</v>
-      </c>
-      <c r="O21" s="45">
-        <v>0</v>
-      </c>
-      <c r="P21" s="45">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="45">
-        <v>0</v>
-      </c>
-      <c r="R21" s="45">
-        <v>0</v>
-      </c>
-      <c r="S21" s="45">
-        <v>0</v>
-      </c>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-      <c r="V21" s="45"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="45"/>
-      <c r="Y21" s="45"/>
-      <c r="Z21" s="45"/>
-      <c r="AA21" s="45"/>
-      <c r="AB21" s="45"/>
-      <c r="AC21" s="45"/>
-      <c r="AD21" s="45"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="45"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="45"/>
-      <c r="AJ21" s="45"/>
-      <c r="AK21" s="45"/>
-      <c r="AL21" s="45"/>
-      <c r="AM21" s="38">
+      <c r="H21" s="44"/>
+      <c r="I21" s="44">
+        <v>0</v>
+      </c>
+      <c r="J21" s="44">
+        <v>0</v>
+      </c>
+      <c r="K21" s="44">
+        <v>0</v>
+      </c>
+      <c r="L21" s="44">
+        <v>0</v>
+      </c>
+      <c r="M21" s="44">
+        <v>0</v>
+      </c>
+      <c r="N21" s="44">
+        <v>0</v>
+      </c>
+      <c r="O21" s="44">
+        <v>0</v>
+      </c>
+      <c r="P21" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="44">
+        <v>0</v>
+      </c>
+      <c r="R21" s="44">
+        <v>0</v>
+      </c>
+      <c r="S21" s="44">
+        <v>0</v>
+      </c>
+      <c r="T21" s="44">
+        <v>0</v>
+      </c>
+      <c r="U21" s="44">
+        <v>0</v>
+      </c>
+      <c r="V21" s="44">
+        <v>0</v>
+      </c>
+      <c r="W21" s="44">
+        <v>0</v>
+      </c>
+      <c r="X21" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="44">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="44">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="44"/>
+      <c r="AD21" s="44"/>
+      <c r="AE21" s="44"/>
+      <c r="AF21" s="44"/>
+      <c r="AG21" s="44"/>
+      <c r="AH21" s="44"/>
+      <c r="AI21" s="44"/>
+      <c r="AJ21" s="44"/>
+      <c r="AK21" s="44"/>
+      <c r="AL21" s="44"/>
+      <c r="AM21" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="48">
+      <c r="C22" s="46"/>
+      <c r="D22" s="47">
         <f>D5+D6+D7+D8+D9+D10+D11+D12+D13+D15+D16+D17+D18+D19+D20+D21</f>
-        <v>146.58815983346437</v>
+        <v>146.00915809647</v>
       </c>
       <c r="E22" s="22">
         <v>0.5</v>
       </c>
       <c r="F22" s="23">
         <f t="shared" si="1"/>
-        <v>269908</v>
-      </c>
-      <c r="G22" s="47"/>
+        <v>498203</v>
+      </c>
+      <c r="G22" s="46"/>
       <c r="H22" s="29"/>
       <c r="I22" s="29">
         <f>9688+3600+4510</f>
@@ -5473,34 +5854,61 @@
         <f>5840+6780+10200+8410</f>
         <v>31230</v>
       </c>
-      <c r="P22" s="49">
+      <c r="P22" s="48">
         <f>7000+7200</f>
         <v>14200</v>
       </c>
-      <c r="Q22" s="49">
+      <c r="Q22" s="48">
         <f>5600+7200+4620+8300</f>
         <v>25720</v>
       </c>
       <c r="R22" s="29">
         <v>26813</v>
       </c>
-      <c r="S22" s="49">
+      <c r="S22" s="48">
         <v>14800</v>
       </c>
-      <c r="T22" s="49"/>
-      <c r="U22" s="49"/>
-      <c r="V22" s="49"/>
-      <c r="W22" s="49"/>
-      <c r="X22" s="49"/>
-      <c r="Y22" s="29"/>
-      <c r="Z22" s="29"/>
-      <c r="AA22" s="49"/>
-      <c r="AB22" s="49"/>
-      <c r="AC22" s="50"/>
-      <c r="AD22" s="50"/>
-      <c r="AE22" s="49"/>
-      <c r="AF22" s="49"/>
-      <c r="AG22" s="49"/>
+      <c r="T22" s="29">
+        <f>9688+3600+4510</f>
+        <v>17798</v>
+      </c>
+      <c r="U22" s="29">
+        <f>6245+5700+6500+6700+3335</f>
+        <v>28480</v>
+      </c>
+      <c r="V22" s="29">
+        <f>7300+4800+10412</f>
+        <v>22512</v>
+      </c>
+      <c r="W22" s="29">
+        <f>9410+7412+12200+7900</f>
+        <v>36922</v>
+      </c>
+      <c r="X22" s="29">
+        <f>6071+3300+6450+5544</f>
+        <v>21365</v>
+      </c>
+      <c r="Y22" s="29">
+        <f>6900+6420+6280+10468</f>
+        <v>30068</v>
+      </c>
+      <c r="Z22" s="29">
+        <f>5840+6780+10200+8410</f>
+        <v>31230</v>
+      </c>
+      <c r="AA22" s="48">
+        <f>7000+7200</f>
+        <v>14200</v>
+      </c>
+      <c r="AB22" s="48">
+        <f>5600+7200+4620+8300</f>
+        <v>25720</v>
+      </c>
+      <c r="AC22" s="49"/>
+      <c r="AD22" s="49"/>
+      <c r="AE22" s="48"/>
+      <c r="AF22" s="48"/>
+      <c r="AG22" s="48"/>
       <c r="AH22" s="29"/>
       <c r="AI22" s="29"/>
       <c r="AJ22" s="29"/>
@@ -5508,571 +5916,571 @@
       <c r="AL22" s="29"/>
       <c r="AM22" s="30">
         <f>SUM(H22:AL22)</f>
-        <v>269908</v>
+        <v>498203</v>
       </c>
     </row>
     <row r="23" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="51"/>
-      <c r="B23" s="52" t="s">
+      <c r="A23" s="50"/>
+      <c r="B23" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53">
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52">
         <f>(+H15+H13+H11+H10+H9+H8+H5+H7+H6)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="53">
+      <c r="I23" s="52">
         <f>(+I15+I13+I11+I10+I9+I8+I5+I7+I6)</f>
         <v>1442</v>
       </c>
-      <c r="J23" s="53">
+      <c r="J23" s="52">
         <f>(+J15+J13+J11+J10+J9+J8+J5+J7+J6)</f>
         <v>4712</v>
       </c>
-      <c r="K23" s="53">
+      <c r="K23" s="52">
         <f t="shared" ref="K23:AI23" si="3">(+K15+K13+K11+K10+K9+K8+K5+K7+K6)</f>
         <v>2386</v>
       </c>
-      <c r="L23" s="53">
+      <c r="L23" s="52">
         <f t="shared" si="3"/>
         <v>2999</v>
       </c>
-      <c r="M23" s="53">
+      <c r="M23" s="52">
         <f t="shared" si="3"/>
         <v>2585</v>
       </c>
-      <c r="N23" s="53">
+      <c r="N23" s="52">
         <f t="shared" si="3"/>
         <v>3601</v>
       </c>
-      <c r="O23" s="53">
+      <c r="O23" s="52">
         <f t="shared" si="3"/>
         <v>4098</v>
       </c>
-      <c r="P23" s="53">
+      <c r="P23" s="52">
         <f t="shared" si="3"/>
         <v>1429</v>
       </c>
-      <c r="Q23" s="53">
+      <c r="Q23" s="52">
         <f t="shared" si="3"/>
         <v>2511</v>
       </c>
-      <c r="R23" s="53">
+      <c r="R23" s="52">
         <f t="shared" si="3"/>
         <v>2752</v>
       </c>
-      <c r="S23" s="53">
+      <c r="S23" s="52">
         <f>(+S15+S13+S11+S10+S9+S8+S5+S7+S6)</f>
         <v>1185</v>
       </c>
-      <c r="T23" s="53">
-        <f t="shared" ref="T23:U23" si="4">(+T15+T13+T11+T10+T9+T8+T5+T7+T6)</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="53">
+      <c r="T23" s="52">
+        <f>(+T15+T13+T11+T10+T9+T8+T5+T7+T6)</f>
+        <v>1442</v>
+      </c>
+      <c r="U23" s="52">
+        <f>(+U15+U13+U11+U10+U9+U8+U5+U7+U6)</f>
+        <v>4712</v>
+      </c>
+      <c r="V23" s="52">
+        <f t="shared" ref="V23:AB23" si="4">(+V15+V13+V11+V10+V9+V8+V5+V7+V6)</f>
+        <v>2386</v>
+      </c>
+      <c r="W23" s="52">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="53">
+        <v>2999</v>
+      </c>
+      <c r="X23" s="52">
+        <f t="shared" si="4"/>
+        <v>2585</v>
+      </c>
+      <c r="Y23" s="52">
+        <f t="shared" si="4"/>
+        <v>3601</v>
+      </c>
+      <c r="Z23" s="52">
+        <f t="shared" si="4"/>
+        <v>4098</v>
+      </c>
+      <c r="AA23" s="52">
+        <f t="shared" si="4"/>
+        <v>1429</v>
+      </c>
+      <c r="AB23" s="52">
+        <f t="shared" si="4"/>
+        <v>2511</v>
+      </c>
+      <c r="AC23" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W23" s="53">
-        <f>(+W15+W13+W11+W10+W9+W8+W5+W7+W6)</f>
-        <v>0</v>
-      </c>
-      <c r="X23" s="53">
+      <c r="AD23" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y23" s="53">
+      <c r="AE23" s="52">
+        <f>(+AE15+AE13+AE11+AE10+AE9+AE8+AE5+AE7+AE6)</f>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="52">
+        <f>(+AF15+AF13+AF11+AF10+AF9+AF8+AF5+AF7+AF6)</f>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="53">
+      <c r="AH23" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA23" s="53">
+      <c r="AI23" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE23" s="53">
-        <f>(+AE15+AE13+AE11+AE10+AE9+AE8+AE5+AE7+AE6)</f>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="53">
-        <f>(+AF15+AF13+AF11+AF10+AF9+AF8+AF5+AF7+AF6)</f>
-        <v>0</v>
-      </c>
-      <c r="AG23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI23" s="53">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="53">
+      <c r="AJ23" s="52">
         <f>(+AJ15+AJ13+AJ11+AJ10+AJ9+AJ8+AJ5+AJ7+AJ6)</f>
         <v>0</v>
       </c>
-      <c r="AK23" s="53">
+      <c r="AK23" s="52">
         <f t="shared" ref="AK23:AL23" si="5">(+AK15+AK13+AK11+AK10+AK9+AK8+AK5+AK7+AK6)</f>
         <v>0</v>
       </c>
-      <c r="AL23" s="53">
+      <c r="AL23" s="52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="54">
+      <c r="AM23" s="53">
         <f>(+AM15+AM13+AM11+AM12+AM10+AM9+AM8+AM5+AM7+AM6)</f>
-        <v>32235</v>
-      </c>
-      <c r="AN23" s="55"/>
-      <c r="AO23" s="56"/>
+        <v>59790</v>
+      </c>
+      <c r="AN23" s="54"/>
+      <c r="AO23" s="55"/>
     </row>
     <row r="24" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="51">
+      <c r="A24" s="50">
         <v>3.45</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="57">
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="56">
         <v>0.05</v>
       </c>
-      <c r="F24" s="52"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="58" t="e">
+      <c r="F24" s="51"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="57" t="e">
         <f>+H23/H22*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="58">
+      <c r="I24" s="57">
         <f t="shared" ref="I24:AL24" si="6">+I23/I22*100</f>
         <v>8.1020339363973495</v>
       </c>
-      <c r="J24" s="58">
+      <c r="J24" s="57">
         <f t="shared" si="6"/>
         <v>16.54494382022472</v>
       </c>
-      <c r="K24" s="58">
+      <c r="K24" s="57">
         <f t="shared" si="6"/>
         <v>10.598791755508174</v>
       </c>
-      <c r="L24" s="58">
+      <c r="L24" s="57">
         <f>+L23/L22*100</f>
         <v>8.1225285737500688</v>
       </c>
-      <c r="M24" s="58">
+      <c r="M24" s="57">
         <f t="shared" si="6"/>
         <v>12.099227708869646</v>
       </c>
-      <c r="N24" s="58">
+      <c r="N24" s="57">
         <f t="shared" si="6"/>
         <v>11.976187308766795</v>
       </c>
-      <c r="O24" s="58">
+      <c r="O24" s="57">
         <f t="shared" si="6"/>
         <v>13.121998078770414</v>
       </c>
-      <c r="P24" s="58">
+      <c r="P24" s="57">
         <f t="shared" si="6"/>
         <v>10.06338028169014</v>
       </c>
-      <c r="Q24" s="58">
+      <c r="Q24" s="57">
         <f t="shared" si="6"/>
         <v>9.7628304821150849</v>
       </c>
-      <c r="R24" s="58">
+      <c r="R24" s="57">
         <f t="shared" si="6"/>
         <v>10.263678066609479</v>
       </c>
-      <c r="S24" s="58">
+      <c r="S24" s="57">
         <f t="shared" si="6"/>
         <v>8.0067567567567561</v>
       </c>
-      <c r="T24" s="58" t="e">
-        <f>+T23/T22*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U24" s="58" t="e">
+      <c r="T24" s="57">
+        <f t="shared" si="6"/>
+        <v>8.1020339363973495</v>
+      </c>
+      <c r="U24" s="57">
+        <f t="shared" si="6"/>
+        <v>16.54494382022472</v>
+      </c>
+      <c r="V24" s="57">
+        <f t="shared" si="6"/>
+        <v>10.598791755508174</v>
+      </c>
+      <c r="W24" s="57">
+        <f>+W23/W22*100</f>
+        <v>8.1225285737500688</v>
+      </c>
+      <c r="X24" s="57">
+        <f t="shared" si="6"/>
+        <v>12.099227708869646</v>
+      </c>
+      <c r="Y24" s="57">
+        <f t="shared" si="6"/>
+        <v>11.976187308766795</v>
+      </c>
+      <c r="Z24" s="57">
+        <f t="shared" si="6"/>
+        <v>13.121998078770414</v>
+      </c>
+      <c r="AA24" s="57">
+        <f t="shared" si="6"/>
+        <v>10.06338028169014</v>
+      </c>
+      <c r="AB24" s="57">
+        <f t="shared" si="6"/>
+        <v>9.7628304821150849</v>
+      </c>
+      <c r="AC24" s="57" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V24" s="58" t="e">
+      <c r="AD24" s="57" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W24" s="58" t="e">
-        <f>+W23/W22*100</f>
+      <c r="AE24" s="57" t="e">
+        <f>+AE23/AE22*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X24" s="58" t="e">
+      <c r="AF24" s="57" t="e">
+        <f>+AF23/AF22*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG24" s="57" t="e">
+        <f>+AG23/AG22*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH24" s="57" t="e">
+        <f>+AH23/AH22*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI24" s="57" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y24" s="58" t="e">
+      <c r="AJ24" s="57" t="e">
+        <f>+AJ23/AJ22*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK24" s="57"/>
+      <c r="AL24" s="57" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE24" s="58" t="e">
-        <f>+AE23/AE22*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF24" s="58" t="e">
-        <f>+AF23/AF22*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG24" s="58" t="e">
-        <f>+AG23/AG22*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH24" s="58" t="e">
-        <f>+AH23/AH22*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ24" s="58" t="e">
-        <f>+AJ23/AJ22*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK24" s="58"/>
-      <c r="AL24" s="58" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM24" s="59">
+      <c r="AM24" s="58">
         <f>+AM23/AM22*100</f>
-        <v>11.942958341360759</v>
-      </c>
-      <c r="AN24" s="60"/>
-      <c r="AO24" s="56"/>
+        <v>12.001132068654744</v>
+      </c>
+      <c r="AN24" s="59"/>
+      <c r="AO24" s="55"/>
     </row>
     <row r="25" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="51"/>
-      <c r="B25" s="61" t="s">
+      <c r="A25" s="50"/>
+      <c r="B25" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="62">
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61">
         <f t="shared" ref="H25:AL25" si="7">(H16+H17+H18+H19+H21)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="62">
+      <c r="I25" s="61">
         <f t="shared" si="7"/>
         <v>399</v>
       </c>
-      <c r="J25" s="62">
+      <c r="J25" s="61">
         <f t="shared" si="7"/>
         <v>154</v>
       </c>
-      <c r="K25" s="62">
+      <c r="K25" s="61">
         <f t="shared" si="7"/>
         <v>187</v>
       </c>
-      <c r="L25" s="62">
+      <c r="L25" s="61">
         <f t="shared" si="7"/>
         <v>244</v>
       </c>
-      <c r="M25" s="62">
+      <c r="M25" s="61">
         <f t="shared" si="7"/>
         <v>113</v>
       </c>
-      <c r="N25" s="62">
+      <c r="N25" s="61">
         <f t="shared" si="7"/>
         <v>106</v>
       </c>
-      <c r="O25" s="62">
+      <c r="O25" s="61">
         <f t="shared" si="7"/>
         <v>127</v>
       </c>
-      <c r="P25" s="62">
+      <c r="P25" s="61">
         <f t="shared" si="7"/>
         <v>39</v>
       </c>
-      <c r="Q25" s="62">
+      <c r="Q25" s="61">
         <f t="shared" si="7"/>
         <v>233</v>
       </c>
-      <c r="R25" s="62">
+      <c r="R25" s="61">
         <f t="shared" si="7"/>
         <v>139</v>
       </c>
-      <c r="S25" s="62">
+      <c r="S25" s="61">
         <f t="shared" si="7"/>
         <v>97</v>
       </c>
-      <c r="T25" s="62">
+      <c r="T25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="62">
+        <v>399</v>
+      </c>
+      <c r="U25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="62">
+        <v>154</v>
+      </c>
+      <c r="V25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="62">
+        <v>187</v>
+      </c>
+      <c r="W25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="62">
+        <v>244</v>
+      </c>
+      <c r="X25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="62">
+        <v>113</v>
+      </c>
+      <c r="Y25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="62">
+        <v>106</v>
+      </c>
+      <c r="Z25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="62">
+        <v>127</v>
+      </c>
+      <c r="AA25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AB25" s="62">
+        <v>39</v>
+      </c>
+      <c r="AB25" s="61">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AC25" s="62">
+        <v>233</v>
+      </c>
+      <c r="AC25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AD25" s="62">
+      <c r="AD25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AE25" s="62">
+      <c r="AE25" s="61">
         <f>(AE16+AE17+AE18+AE19+AE21)</f>
         <v>0</v>
       </c>
-      <c r="AF25" s="62">
+      <c r="AF25" s="61">
         <f>(AF16+AF17+AF18+AF19+AF21)</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="62">
+      <c r="AG25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="62">
+      <c r="AH25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI25" s="62">
+      <c r="AI25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AJ25" s="62">
+      <c r="AJ25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK25" s="62"/>
-      <c r="AL25" s="62">
+      <c r="AK25" s="61"/>
+      <c r="AL25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM25" s="30">
         <f>SUM(H25:AL25)</f>
-        <v>1838</v>
-      </c>
-      <c r="AN25" s="60"/>
-      <c r="AO25" s="56"/>
+        <v>3440</v>
+      </c>
+      <c r="AN25" s="59"/>
+      <c r="AO25" s="55"/>
     </row>
     <row r="26" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="51">
+      <c r="A26" s="50">
         <v>6.58</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="63">
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="62">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="64" t="e">
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="63" t="e">
         <f>(H25/H22)*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I26" s="64">
+      <c r="I26" s="63">
         <f t="shared" ref="I26:AL26" si="8">(I25/I22)*100</f>
         <v>2.2418249241487809</v>
       </c>
-      <c r="J26" s="64">
+      <c r="J26" s="63">
         <f t="shared" si="8"/>
         <v>0.5407303370786517</v>
       </c>
-      <c r="K26" s="64">
+      <c r="K26" s="63">
         <f t="shared" si="8"/>
         <v>0.83066808813077475</v>
       </c>
-      <c r="L26" s="64">
+      <c r="L26" s="63">
         <f t="shared" si="8"/>
         <v>0.6608526082010725</v>
       </c>
-      <c r="M26" s="64">
+      <c r="M26" s="63">
         <f t="shared" si="8"/>
         <v>0.5289024104844372</v>
       </c>
-      <c r="N26" s="64">
+      <c r="N26" s="63">
         <f t="shared" si="8"/>
         <v>0.35253425568710922</v>
       </c>
-      <c r="O26" s="64">
+      <c r="O26" s="63">
         <f t="shared" si="8"/>
         <v>0.40666026256804355</v>
       </c>
-      <c r="P26" s="64">
+      <c r="P26" s="63">
         <f t="shared" si="8"/>
         <v>0.27464788732394368</v>
       </c>
-      <c r="Q26" s="64">
+      <c r="Q26" s="63">
         <f t="shared" si="8"/>
         <v>0.90590979782270609</v>
       </c>
-      <c r="R26" s="64">
+      <c r="R26" s="63">
         <f t="shared" si="8"/>
         <v>0.51840525118412717</v>
       </c>
-      <c r="S26" s="64">
+      <c r="S26" s="63">
         <f t="shared" si="8"/>
         <v>0.65540540540540537</v>
       </c>
-      <c r="T26" s="64" t="e">
+      <c r="T26" s="63">
+        <f t="shared" si="8"/>
+        <v>2.2418249241487809</v>
+      </c>
+      <c r="U26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.5407303370786517</v>
+      </c>
+      <c r="V26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.83066808813077475</v>
+      </c>
+      <c r="W26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.6608526082010725</v>
+      </c>
+      <c r="X26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.5289024104844372</v>
+      </c>
+      <c r="Y26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.35253425568710922</v>
+      </c>
+      <c r="Z26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.40666026256804355</v>
+      </c>
+      <c r="AA26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.27464788732394368</v>
+      </c>
+      <c r="AB26" s="63">
+        <f t="shared" si="8"/>
+        <v>0.90590979782270609</v>
+      </c>
+      <c r="AC26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U26" s="64" t="e">
+      <c r="AD26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V26" s="64" t="e">
+      <c r="AE26" s="63" t="e">
+        <f>(AE25/AE22)*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF26" s="63" t="e">
+        <f>(AF25/AF22)*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG26" s="63" t="e">
+        <f>(AG25/AG22)*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W26" s="64" t="e">
+      <c r="AI26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X26" s="64" t="e">
+      <c r="AJ26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y26" s="64" t="e">
+      <c r="AK26" s="63"/>
+      <c r="AL26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE26" s="64" t="e">
-        <f>(AE25/AE22)*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF26" s="64" t="e">
-        <f>(AF25/AF22)*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG26" s="64" t="e">
-        <f>(AG25/AG22)*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK26" s="64"/>
-      <c r="AL26" s="64" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AM26" s="59">
+      <c r="AM26" s="58">
         <f>(AM25/AM22*100)</f>
-        <v>0.68097277590882821</v>
-      </c>
-      <c r="AN26" s="65"/>
-      <c r="AO26" s="56"/>
+        <v>0.69048159083746985</v>
+      </c>
+      <c r="AN26" s="64"/>
+      <c r="AO26" s="55"/>
     </row>
     <row r="27" spans="1:41" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
@@ -6081,7 +6489,7 @@
       <c r="L27">
         <v>5.1100000000000003</v>
       </c>
-      <c r="R27" s="66">
+      <c r="R27" s="65">
         <f>2400+7336+5346+8095+6797+4800+5400</f>
         <v>40174</v>
       </c>
@@ -6090,91 +6498,91 @@
       <c r="B28" t="s">
         <v>35</v>
       </c>
-      <c r="X28" s="67"/>
+      <c r="X28" s="66"/>
     </row>
     <row r="29" spans="1:41" ht="71.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:41" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AI30" s="68"/>
+      <c r="AI30" s="67"/>
     </row>
     <row r="31" spans="1:41" ht="71.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:41" ht="71.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="Z32" s="69" t="s">
+      <c r="Z32" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="AA32" s="70"/>
-      <c r="AB32" s="71"/>
-      <c r="AC32" s="71"/>
+      <c r="AA32" s="69"/>
+      <c r="AB32" s="70"/>
+      <c r="AC32" s="70"/>
     </row>
     <row r="33" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="Z33" s="69" t="s">
+      <c r="Z33" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="71"/>
-      <c r="AC33" s="72"/>
-      <c r="AD33" s="73"/>
-      <c r="AE33" s="73"/>
+      <c r="AA33" s="69"/>
+      <c r="AB33" s="70"/>
+      <c r="AC33" s="71"/>
+      <c r="AD33" s="72"/>
+      <c r="AE33" s="72"/>
     </row>
     <row r="34" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="Z34" s="69" t="s">
+      <c r="Z34" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="71"/>
-      <c r="AC34" s="72"/>
-      <c r="AD34" s="72"/>
-      <c r="AE34" s="72"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="70"/>
+      <c r="AC34" s="71"/>
+      <c r="AD34" s="71"/>
+      <c r="AE34" s="71"/>
     </row>
     <row r="35" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="Z35" s="74"/>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="71"/>
-      <c r="AC35" s="72"/>
-      <c r="AD35" s="72"/>
-      <c r="AE35" s="72"/>
+      <c r="Z35" s="73"/>
+      <c r="AA35" s="73"/>
+      <c r="AB35" s="70"/>
+      <c r="AC35" s="71"/>
+      <c r="AD35" s="71"/>
+      <c r="AE35" s="71"/>
     </row>
     <row r="36" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="Z36" s="74"/>
-      <c r="AA36" s="74"/>
-      <c r="AB36" s="71"/>
-      <c r="AC36" s="72"/>
-      <c r="AD36" s="72"/>
-      <c r="AE36" s="72"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="73"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="71"/>
+      <c r="AD36" s="71"/>
+      <c r="AE36" s="71"/>
     </row>
     <row r="37" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC37" s="72"/>
-      <c r="AD37" s="72"/>
-      <c r="AE37" s="72"/>
+      <c r="AC37" s="71"/>
+      <c r="AD37" s="71"/>
+      <c r="AE37" s="71"/>
     </row>
     <row r="38" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC38" s="72"/>
-      <c r="AD38" s="72"/>
-      <c r="AE38" s="72"/>
+      <c r="AC38" s="71"/>
+      <c r="AD38" s="71"/>
+      <c r="AE38" s="71"/>
     </row>
     <row r="39" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC39" s="72"/>
-      <c r="AD39" s="72"/>
-      <c r="AE39" s="72"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="71"/>
+      <c r="AE39" s="71"/>
     </row>
     <row r="40" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC40" s="72"/>
-      <c r="AD40" s="72"/>
-      <c r="AE40" s="72"/>
+      <c r="AC40" s="71"/>
+      <c r="AD40" s="71"/>
+      <c r="AE40" s="71"/>
     </row>
     <row r="41" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC41" s="72"/>
-      <c r="AD41" s="72"/>
-      <c r="AE41" s="72"/>
+      <c r="AC41" s="71"/>
+      <c r="AD41" s="71"/>
+      <c r="AE41" s="71"/>
     </row>
     <row r="42" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC42" s="72"/>
-      <c r="AD42" s="72"/>
-      <c r="AE42" s="72"/>
+      <c r="AC42" s="71"/>
+      <c r="AD42" s="71"/>
+      <c r="AE42" s="71"/>
     </row>
     <row r="43" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AC43" s="75"/>
-      <c r="AD43" s="75"/>
-      <c r="AE43" s="75"/>
+      <c r="AC43" s="74"/>
+      <c r="AD43" s="74"/>
+      <c r="AE43" s="74"/>
     </row>
     <row r="44" spans="26:31" ht="71.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -6182,23 +6590,6 @@
     <mergeCell ref="H1:X1"/>
     <mergeCell ref="AJ1:AM1"/>
   </mergeCells>
-  <conditionalFormatting sqref="U23">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V5">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$C$5&lt;$V$5</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM22">
     <cfRule type="top10" dxfId="0" priority="2" percent="1" rank="10"/>
   </conditionalFormatting>

--- a/rejection_data.xlsx
+++ b/rejection_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Admin\Desktop\PistonRodPortal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CE5709-106C-4B2A-A94A-2D6E9B33672E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60D348E-FEBD-4F02-9CE4-36648D82312E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2FF8ABF7-B34E-4442-953A-A8AB69CBC555}"/>
   </bookViews>
@@ -708,7 +708,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -716,13 +716,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1217,18 +1210,6 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>12.099227708869646</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>11.976187308766795</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>13.121998078770414</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>10.06338028169014</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>9.7628304821150849</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -1700,18 +1681,6 @@
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0.5289024104844372</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.35253425568710922</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.40666026256804355</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.27464788732394368</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.90590979782270609</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -3872,14 +3841,14 @@
       </c>
       <c r="D5" s="21">
         <f>AM5/AM22*100</f>
-        <v>1.396017286126338</v>
+        <v>1.3597491089083971</v>
       </c>
       <c r="E5" s="22">
         <v>1.74</v>
       </c>
       <c r="F5" s="23">
         <f>SUM(H5:AL5)</f>
-        <v>6955</v>
+        <v>5398</v>
       </c>
       <c r="G5" s="24">
         <v>15722</v>
@@ -3947,22 +3916,10 @@
         <f>116+80+84+87</f>
         <v>367</v>
       </c>
-      <c r="Y5" s="25">
-        <f>56+87+40+188</f>
-        <v>371</v>
-      </c>
-      <c r="Z5" s="25">
-        <f>251+177+83+134</f>
-        <v>645</v>
-      </c>
-      <c r="AA5" s="25">
-        <f>122+54</f>
-        <v>176</v>
-      </c>
-      <c r="AB5" s="25">
-        <f>96+65+74+130</f>
-        <v>365</v>
-      </c>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
       <c r="AC5" s="26"/>
       <c r="AD5" s="26"/>
       <c r="AE5" s="25"/>
@@ -3975,7 +3932,7 @@
       <c r="AL5" s="25"/>
       <c r="AM5" s="25">
         <f>SUM(H5:AL5)</f>
-        <v>6955</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="6" spans="2:175" s="31" customFormat="1" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4049,18 +4006,10 @@
       <c r="X6" s="29">
         <v>0</v>
       </c>
-      <c r="Y6" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="29">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="29">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="29">
-        <v>0</v>
-      </c>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
       <c r="AC6" s="29"/>
       <c r="AD6" s="29"/>
       <c r="AE6" s="29"/>
@@ -4220,7 +4169,7 @@
       </c>
       <c r="D7" s="21">
         <f>AM7/AM24*100</f>
-        <v>133.32075597926075</v>
+        <v>134.21574220813523</v>
       </c>
       <c r="E7" s="22">
         <v>0.33</v>
@@ -4281,18 +4230,10 @@
       <c r="X7" s="33">
         <v>0</v>
       </c>
-      <c r="Y7" s="33">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="33">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="33">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="33">
-        <v>0</v>
-      </c>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="33"/>
+      <c r="AB7" s="33"/>
       <c r="AC7" s="34"/>
       <c r="AD7" s="34"/>
       <c r="AE7" s="33"/>
@@ -4318,14 +4259,14 @@
       </c>
       <c r="D8" s="21">
         <f>AM8/AM22*100</f>
-        <v>1.7366414895133107</v>
+        <v>1.7527110596118241</v>
       </c>
       <c r="E8" s="22">
         <v>0.51</v>
       </c>
       <c r="F8" s="23">
         <f t="shared" si="1"/>
-        <v>8652</v>
+        <v>6958</v>
       </c>
       <c r="G8" s="24">
         <v>4592</v>
@@ -4393,22 +4334,10 @@
         <f>250+44+98</f>
         <v>392</v>
       </c>
-      <c r="Y8" s="30">
-        <f>210+111+377</f>
-        <v>698</v>
-      </c>
-      <c r="Z8" s="30">
-        <f>115+129+90+211</f>
-        <v>545</v>
-      </c>
-      <c r="AA8" s="36">
-        <f>136+0</f>
-        <v>136</v>
-      </c>
-      <c r="AB8" s="30">
-        <f>158+87+70</f>
-        <v>315</v>
-      </c>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="36"/>
+      <c r="AB8" s="30"/>
       <c r="AC8" s="38"/>
       <c r="AD8" s="38"/>
       <c r="AE8" s="30"/>
@@ -4421,7 +4350,7 @@
       <c r="AL8" s="30"/>
       <c r="AM8" s="30">
         <f t="shared" si="2"/>
-        <v>8652</v>
+        <v>6958</v>
       </c>
     </row>
     <row r="9" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4434,14 +4363,14 @@
       </c>
       <c r="D9" s="21">
         <f>AM9/AM22*100</f>
-        <v>0.29606405421083376</v>
+        <v>0.30253032230436921</v>
       </c>
       <c r="E9" s="22">
         <v>0.35</v>
       </c>
       <c r="F9" s="23">
         <f t="shared" si="1"/>
-        <v>1475</v>
+        <v>1201</v>
       </c>
       <c r="G9" s="24">
         <v>5267</v>
@@ -4509,22 +4438,10 @@
         <f>16+19+24</f>
         <v>59</v>
       </c>
-      <c r="Y9" s="30">
-        <f>14+40+39</f>
-        <v>93</v>
-      </c>
-      <c r="Z9" s="30">
-        <f>20+3+50+13</f>
-        <v>86</v>
-      </c>
-      <c r="AA9" s="30">
-        <f>12+15</f>
-        <v>27</v>
-      </c>
-      <c r="AB9" s="30">
-        <f>2+7+59</f>
-        <v>68</v>
-      </c>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
       <c r="AC9" s="38"/>
       <c r="AD9" s="38"/>
       <c r="AE9" s="30"/>
@@ -4537,7 +4454,7 @@
       <c r="AL9" s="30"/>
       <c r="AM9" s="30">
         <f t="shared" si="2"/>
-        <v>1475</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="10" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4550,14 +4467,14 @@
       </c>
       <c r="D10" s="21">
         <f>AM10/AM22*100</f>
-        <v>0.18105069620215053</v>
+        <v>0.14685693414108844</v>
       </c>
       <c r="E10" s="22">
         <v>0.88</v>
       </c>
       <c r="F10" s="23">
         <f t="shared" si="1"/>
-        <v>902</v>
+        <v>583</v>
       </c>
       <c r="G10" s="24">
         <v>7891</v>
@@ -4615,20 +4532,10 @@
       <c r="X10" s="30">
         <v>10</v>
       </c>
-      <c r="Y10" s="30">
-        <f>27+8</f>
-        <v>35</v>
-      </c>
-      <c r="Z10" s="30">
-        <f>16+138+31</f>
-        <v>185</v>
-      </c>
-      <c r="AA10" s="30">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="30">
-        <v>94</v>
-      </c>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
       <c r="AC10" s="38"/>
       <c r="AD10" s="38"/>
       <c r="AE10" s="30"/>
@@ -4641,7 +4548,7 @@
       <c r="AL10" s="30"/>
       <c r="AM10" s="30">
         <f t="shared" si="2"/>
-        <v>902</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4654,14 +4561,14 @@
       </c>
       <c r="D11" s="21">
         <f>AM11/AM22*100</f>
-        <v>5.8729072285795141</v>
+        <v>5.8536216733629738</v>
       </c>
       <c r="E11" s="22">
         <v>0.59</v>
       </c>
       <c r="F11" s="23">
         <f t="shared" si="1"/>
-        <v>29259</v>
+        <v>23238</v>
       </c>
       <c r="G11" s="39">
         <v>5291</v>
@@ -4729,22 +4636,10 @@
         <f>742+69+205+131</f>
         <v>1147</v>
       </c>
-      <c r="Y11" s="30">
-        <f>232+355+700+231</f>
-        <v>1518</v>
-      </c>
-      <c r="Z11" s="30">
-        <f>180+550+650+858</f>
-        <v>2238</v>
-      </c>
-      <c r="AA11" s="30">
-        <f>500+486</f>
-        <v>986</v>
-      </c>
-      <c r="AB11" s="30">
-        <f>300+350+139+490</f>
-        <v>1279</v>
-      </c>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
       <c r="AC11" s="38"/>
       <c r="AD11" s="38"/>
       <c r="AE11" s="30"/>
@@ -4757,7 +4652,7 @@
       <c r="AL11" s="30"/>
       <c r="AM11" s="30">
         <f t="shared" si="2"/>
-        <v>29259</v>
+        <v>23238</v>
       </c>
     </row>
     <row r="12" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4770,14 +4665,14 @@
       </c>
       <c r="D12" s="21">
         <f>AM12/AM22*100</f>
-        <v>0.86852146614934067</v>
+        <v>0.88189730090557572</v>
       </c>
       <c r="E12" s="22">
         <v>0.57999999999999996</v>
       </c>
       <c r="F12" s="23">
         <f t="shared" si="1"/>
-        <v>4327</v>
+        <v>3501</v>
       </c>
       <c r="G12" s="39">
         <v>5214</v>
@@ -4841,20 +4736,10 @@
         <f>100+41</f>
         <v>141</v>
       </c>
-      <c r="Y12" s="30">
-        <f>137+89+100</f>
-        <v>326</v>
-      </c>
-      <c r="Z12" s="30">
-        <f>100+200</f>
-        <v>300</v>
-      </c>
-      <c r="AA12" s="30">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="30">
-        <v>200</v>
-      </c>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
       <c r="AC12" s="38"/>
       <c r="AD12" s="38"/>
       <c r="AE12" s="30"/>
@@ -4867,7 +4752,7 @@
       <c r="AL12" s="41"/>
       <c r="AM12" s="41">
         <f t="shared" si="2"/>
-        <v>4327</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="13" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4880,14 +4765,14 @@
       </c>
       <c r="D13" s="21">
         <f>AM13/AM22*100</f>
-        <v>1.2727743510175571</v>
+        <v>1.2242276156529845</v>
       </c>
       <c r="E13" s="22">
         <v>0.36</v>
       </c>
       <c r="F13" s="23">
         <f t="shared" si="1"/>
-        <v>6341</v>
+        <v>4860</v>
       </c>
       <c r="G13" s="39">
         <v>3248</v>
@@ -4955,22 +4840,10 @@
         <f>0+286+201+39+30</f>
         <v>556</v>
       </c>
-      <c r="Y13" s="30">
-        <f>464+149+56+60</f>
-        <v>729</v>
-      </c>
-      <c r="Z13" s="30">
-        <f>249+63+40</f>
-        <v>352</v>
-      </c>
-      <c r="AA13" s="30">
-        <f>26+40</f>
-        <v>66</v>
-      </c>
-      <c r="AB13" s="30">
-        <f>30+25+40+239</f>
-        <v>334</v>
-      </c>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
       <c r="AC13" s="38"/>
       <c r="AD13" s="38"/>
       <c r="AE13" s="30"/>
@@ -4983,7 +4856,7 @@
       <c r="AL13" s="30"/>
       <c r="AM13" s="30">
         <f t="shared" si="2"/>
-        <v>6341</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="14" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4998,7 +4871,7 @@
       <c r="E14" s="22"/>
       <c r="F14" s="23">
         <f t="shared" si="1"/>
-        <v>704</v>
+        <v>352</v>
       </c>
       <c r="G14" s="39"/>
       <c r="H14" s="30"/>
@@ -5051,19 +4924,10 @@
       <c r="X14" s="30">
         <v>0</v>
       </c>
-      <c r="Y14" s="30">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="30">
-        <f>40+63+249</f>
-        <v>352</v>
-      </c>
-      <c r="AA14" s="30">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="30">
-        <v>0</v>
-      </c>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
       <c r="AC14" s="38"/>
       <c r="AD14" s="38"/>
       <c r="AE14" s="30"/>
@@ -5076,7 +4940,7 @@
       <c r="AL14" s="30"/>
       <c r="AM14" s="30">
         <f t="shared" si="2"/>
-        <v>704</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5089,14 +4953,14 @@
       </c>
       <c r="D15" s="21">
         <f>AM15/AM22*100</f>
-        <v>0.37394395457273444</v>
+        <v>0.39548093756691061</v>
       </c>
       <c r="E15" s="22">
         <v>0.17</v>
       </c>
       <c r="F15" s="23">
         <f t="shared" si="1"/>
-        <v>1863</v>
+        <v>1570</v>
       </c>
       <c r="G15" s="39">
         <v>1489</v>
@@ -5164,22 +5028,10 @@
         <f>5+23+26</f>
         <v>54</v>
       </c>
-      <c r="Y15" s="30">
-        <f>103+4+50</f>
-        <v>157</v>
-      </c>
-      <c r="Z15" s="30">
-        <f>20+27</f>
-        <v>47</v>
-      </c>
-      <c r="AA15" s="30">
-        <f>10+23</f>
-        <v>33</v>
-      </c>
-      <c r="AB15" s="30">
-        <f>16+20+20</f>
-        <v>56</v>
-      </c>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="30"/>
       <c r="AC15" s="38"/>
       <c r="AD15" s="38"/>
       <c r="AE15" s="30"/>
@@ -5192,7 +5044,7 @@
       <c r="AL15" s="30"/>
       <c r="AM15" s="30">
         <f t="shared" si="2"/>
-        <v>1863</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="16" spans="2:175" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5265,18 +5117,10 @@
       <c r="X16" s="37">
         <v>0</v>
       </c>
-      <c r="Y16" s="37">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="37">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="37">
-        <v>0</v>
-      </c>
+      <c r="Y16" s="37"/>
+      <c r="Z16" s="37"/>
+      <c r="AA16" s="37"/>
+      <c r="AB16" s="37"/>
       <c r="AC16" s="37"/>
       <c r="AD16" s="37"/>
       <c r="AE16" s="37"/>
@@ -5302,7 +5146,7 @@
       </c>
       <c r="D17" s="21">
         <f>AM17/AM22*100</f>
-        <v>7.0252487439858855E-3</v>
+        <v>8.8164540221922737E-3</v>
       </c>
       <c r="E17" s="22">
         <v>0.01</v>
@@ -5363,18 +5207,10 @@
       <c r="X17" s="37">
         <v>0</v>
       </c>
-      <c r="Y17" s="37">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="37">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="37">
-        <v>0</v>
-      </c>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="37"/>
+      <c r="AA17" s="37"/>
+      <c r="AB17" s="37"/>
       <c r="AC17" s="43"/>
       <c r="AD17" s="43"/>
       <c r="AE17" s="37"/>
@@ -5400,14 +5236,14 @@
       </c>
       <c r="D18" s="21">
         <f>AM18/AM22*100</f>
-        <v>0.22942455183931049</v>
+        <v>0.24308223232615842</v>
       </c>
       <c r="E18" s="22">
         <v>0.21</v>
       </c>
       <c r="F18" s="23">
         <f t="shared" si="1"/>
-        <v>1143</v>
+        <v>965</v>
       </c>
       <c r="G18" s="39">
         <v>1872</v>
@@ -5475,22 +5311,10 @@
         <f>6+26+26</f>
         <v>58</v>
       </c>
-      <c r="Y18" s="37">
-        <f>48+22</f>
-        <v>70</v>
-      </c>
-      <c r="Z18" s="37">
-        <f>16+20</f>
-        <v>36</v>
-      </c>
-      <c r="AA18" s="37">
-        <f>28+11</f>
-        <v>39</v>
-      </c>
-      <c r="AB18" s="37">
-        <f>20+13</f>
-        <v>33</v>
-      </c>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="37"/>
+      <c r="AA18" s="37"/>
+      <c r="AB18" s="37"/>
       <c r="AC18" s="43"/>
       <c r="AD18" s="43"/>
       <c r="AE18" s="37"/>
@@ -5503,7 +5327,7 @@
       <c r="AL18" s="37"/>
       <c r="AM18" s="37">
         <f t="shared" si="2"/>
-        <v>1143</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5516,14 +5340,14 @@
       </c>
       <c r="D19" s="21">
         <f>AM19/AM22*100</f>
-        <v>0.45403179025417351</v>
+        <v>0.48742395808405853</v>
       </c>
       <c r="E19" s="22">
         <v>0.28000000000000003</v>
       </c>
       <c r="F19" s="23">
         <f t="shared" si="1"/>
-        <v>2262</v>
+        <v>1935</v>
       </c>
       <c r="G19" s="39">
         <v>2502</v>
@@ -5585,20 +5409,10 @@
       <c r="X19" s="44">
         <v>55</v>
       </c>
-      <c r="Y19" s="44">
-        <f>35+1</f>
-        <v>36</v>
-      </c>
-      <c r="Z19" s="44">
-        <f>41+50</f>
-        <v>91</v>
-      </c>
-      <c r="AA19" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="37">
-        <v>200</v>
-      </c>
+      <c r="Y19" s="44"/>
+      <c r="Z19" s="44"/>
+      <c r="AA19" s="37"/>
+      <c r="AB19" s="37"/>
       <c r="AC19" s="43"/>
       <c r="AD19" s="43"/>
       <c r="AE19" s="37"/>
@@ -5611,7 +5425,7 @@
       <c r="AL19" s="37"/>
       <c r="AM19" s="37">
         <f t="shared" si="2"/>
-        <v>2262</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="20" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5684,18 +5498,10 @@
       <c r="X20" s="44">
         <v>0</v>
       </c>
-      <c r="Y20" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="44">
-        <v>0</v>
-      </c>
+      <c r="Y20" s="44"/>
+      <c r="Z20" s="44"/>
+      <c r="AA20" s="44"/>
+      <c r="AB20" s="44"/>
       <c r="AC20" s="44"/>
       <c r="AD20" s="44"/>
       <c r="AE20" s="44"/>
@@ -5781,18 +5587,10 @@
       <c r="X21" s="44">
         <v>0</v>
       </c>
-      <c r="Y21" s="44">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="44">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="44">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="44">
-        <v>0</v>
-      </c>
+      <c r="Y21" s="44"/>
+      <c r="Z21" s="44"/>
+      <c r="AA21" s="44"/>
+      <c r="AB21" s="44"/>
       <c r="AC21" s="44"/>
       <c r="AD21" s="44"/>
       <c r="AE21" s="44"/>
@@ -5815,14 +5613,14 @@
       <c r="C22" s="46"/>
       <c r="D22" s="47">
         <f>D5+D6+D7+D8+D9+D10+D11+D12+D13+D15+D16+D17+D18+D19+D20+D21</f>
-        <v>146.00915809647</v>
+        <v>146.8721398050217</v>
       </c>
       <c r="E22" s="22">
         <v>0.5</v>
       </c>
       <c r="F22" s="23">
         <f t="shared" si="1"/>
-        <v>498203</v>
+        <v>396985</v>
       </c>
       <c r="G22" s="46"/>
       <c r="H22" s="29"/>
@@ -5888,22 +5686,10 @@
         <f>6071+3300+6450+5544</f>
         <v>21365</v>
       </c>
-      <c r="Y22" s="29">
-        <f>6900+6420+6280+10468</f>
-        <v>30068</v>
-      </c>
-      <c r="Z22" s="29">
-        <f>5840+6780+10200+8410</f>
-        <v>31230</v>
-      </c>
-      <c r="AA22" s="48">
-        <f>7000+7200</f>
-        <v>14200</v>
-      </c>
-      <c r="AB22" s="48">
-        <f>5600+7200+4620+8300</f>
-        <v>25720</v>
-      </c>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+      <c r="AA22" s="48"/>
+      <c r="AB22" s="48"/>
       <c r="AC22" s="49"/>
       <c r="AD22" s="49"/>
       <c r="AE22" s="48"/>
@@ -5916,7 +5702,7 @@
       <c r="AL22" s="29"/>
       <c r="AM22" s="30">
         <f>SUM(H22:AL22)</f>
-        <v>498203</v>
+        <v>396985</v>
       </c>
     </row>
     <row r="23" spans="1:41" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5997,22 +5783,10 @@
         <f t="shared" si="4"/>
         <v>2585</v>
       </c>
-      <c r="Y23" s="52">
-        <f t="shared" si="4"/>
-        <v>3601</v>
-      </c>
-      <c r="Z23" s="52">
-        <f t="shared" si="4"/>
-        <v>4098</v>
-      </c>
-      <c r="AA23" s="52">
-        <f t="shared" si="4"/>
-        <v>1429</v>
-      </c>
-      <c r="AB23" s="52">
-        <f t="shared" si="4"/>
-        <v>2511</v>
-      </c>
+      <c r="Y23" s="52"/>
+      <c r="Z23" s="52"/>
+      <c r="AA23" s="52"/>
+      <c r="AB23" s="52"/>
       <c r="AC23" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -6055,7 +5829,7 @@
       </c>
       <c r="AM23" s="53">
         <f>(+AM15+AM13+AM11+AM12+AM10+AM9+AM8+AM5+AM7+AM6)</f>
-        <v>59790</v>
+        <v>47325</v>
       </c>
       <c r="AN23" s="54"/>
       <c r="AO23" s="55"/>
@@ -6142,22 +5916,10 @@
         <f t="shared" si="6"/>
         <v>12.099227708869646</v>
       </c>
-      <c r="Y24" s="57">
-        <f t="shared" si="6"/>
-        <v>11.976187308766795</v>
-      </c>
-      <c r="Z24" s="57">
-        <f t="shared" si="6"/>
-        <v>13.121998078770414</v>
-      </c>
-      <c r="AA24" s="57">
-        <f t="shared" si="6"/>
-        <v>10.06338028169014</v>
-      </c>
-      <c r="AB24" s="57">
-        <f t="shared" si="6"/>
-        <v>9.7628304821150849</v>
-      </c>
+      <c r="Y24" s="57"/>
+      <c r="Z24" s="57"/>
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="57"/>
       <c r="AC24" s="57" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -6197,7 +5959,7 @@
       </c>
       <c r="AM24" s="58">
         <f>+AM23/AM22*100</f>
-        <v>12.001132068654744</v>
+        <v>11.921105331435697</v>
       </c>
       <c r="AN24" s="59"/>
       <c r="AO24" s="55"/>
@@ -6280,22 +6042,10 @@
         <f t="shared" si="7"/>
         <v>113</v>
       </c>
-      <c r="Y25" s="61">
-        <f t="shared" si="7"/>
-        <v>106</v>
-      </c>
-      <c r="Z25" s="61">
-        <f t="shared" si="7"/>
-        <v>127</v>
-      </c>
-      <c r="AA25" s="61">
-        <f t="shared" si="7"/>
-        <v>39</v>
-      </c>
-      <c r="AB25" s="61">
-        <f t="shared" si="7"/>
-        <v>233</v>
-      </c>
+      <c r="Y25" s="61"/>
+      <c r="Z25" s="61"/>
+      <c r="AA25" s="61"/>
+      <c r="AB25" s="61"/>
       <c r="AC25" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -6335,7 +6085,7 @@
       </c>
       <c r="AM25" s="30">
         <f>SUM(H25:AL25)</f>
-        <v>3440</v>
+        <v>2935</v>
       </c>
       <c r="AN25" s="59"/>
       <c r="AO25" s="55"/>
@@ -6422,22 +6172,10 @@
         <f t="shared" si="8"/>
         <v>0.5289024104844372</v>
       </c>
-      <c r="Y26" s="63">
-        <f t="shared" si="8"/>
-        <v>0.35253425568710922</v>
-      </c>
-      <c r="Z26" s="63">
-        <f t="shared" si="8"/>
-        <v>0.40666026256804355</v>
-      </c>
-      <c r="AA26" s="63">
-        <f t="shared" si="8"/>
-        <v>0.27464788732394368</v>
-      </c>
-      <c r="AB26" s="63">
-        <f t="shared" si="8"/>
-        <v>0.90590979782270609</v>
-      </c>
+      <c r="Y26" s="63"/>
+      <c r="Z26" s="63"/>
+      <c r="AA26" s="63"/>
+      <c r="AB26" s="63"/>
       <c r="AC26" s="63" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -6477,7 +6215,7 @@
       </c>
       <c r="AM26" s="58">
         <f>(AM25/AM22*100)</f>
-        <v>0.69048159083746985</v>
+        <v>0.73932264443240936</v>
       </c>
       <c r="AN26" s="64"/>
       <c r="AO26" s="55"/>
